--- a/prediction_market_volumes.xlsx
+++ b/prediction_market_volumes.xlsx
@@ -17,11 +17,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00_-"/>
-    <numFmt numFmtId="167" formatCode="$#,##0"/>
+    <numFmt numFmtId="166" formatCode="$#,##0"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -72,7 +71,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,91 +479,91 @@
         </is>
       </c>
       <c r="B1" s="2" t="n">
-        <v>46235</v>
+        <v>45383</v>
       </c>
       <c r="C1" s="2" t="n">
-        <v>46204</v>
+        <v>45413</v>
       </c>
       <c r="D1" s="2" t="n">
-        <v>46174</v>
+        <v>45444</v>
       </c>
       <c r="E1" s="2" t="n">
-        <v>46143</v>
+        <v>45474</v>
       </c>
       <c r="F1" s="2" t="n">
-        <v>46113</v>
+        <v>45505</v>
       </c>
       <c r="G1" s="2" t="n">
-        <v>46082</v>
+        <v>45536</v>
       </c>
       <c r="H1" s="2" t="n">
-        <v>46054</v>
+        <v>45566</v>
       </c>
       <c r="I1" s="2" t="n">
-        <v>46023</v>
+        <v>45597</v>
       </c>
       <c r="J1" s="2" t="n">
-        <v>45992</v>
+        <v>45627</v>
       </c>
       <c r="K1" s="2" t="n">
-        <v>45962</v>
+        <v>45658</v>
       </c>
       <c r="L1" s="2" t="n">
-        <v>45931</v>
+        <v>45689</v>
       </c>
       <c r="M1" s="2" t="n">
-        <v>45901</v>
+        <v>45717</v>
       </c>
       <c r="N1" s="2" t="n">
-        <v>45870</v>
+        <v>45748</v>
       </c>
       <c r="O1" s="2" t="n">
-        <v>45839</v>
+        <v>45778</v>
       </c>
       <c r="P1" s="2" t="n">
         <v>45809</v>
       </c>
       <c r="Q1" s="2" t="n">
-        <v>45778</v>
+        <v>45839</v>
       </c>
       <c r="R1" s="2" t="n">
-        <v>45748</v>
+        <v>45870</v>
       </c>
       <c r="S1" s="2" t="n">
-        <v>45717</v>
+        <v>45901</v>
       </c>
       <c r="T1" s="2" t="n">
-        <v>45689</v>
+        <v>45931</v>
       </c>
       <c r="U1" s="2" t="n">
-        <v>45658</v>
+        <v>45962</v>
       </c>
       <c r="V1" s="2" t="n">
-        <v>45627</v>
+        <v>45992</v>
       </c>
       <c r="W1" s="2" t="n">
-        <v>45597</v>
+        <v>46023</v>
       </c>
       <c r="X1" s="2" t="n">
-        <v>45566</v>
+        <v>46054</v>
       </c>
       <c r="Y1" s="2" t="n">
-        <v>45536</v>
+        <v>46082</v>
       </c>
       <c r="Z1" s="2" t="n">
-        <v>45505</v>
+        <v>46113</v>
       </c>
       <c r="AA1" s="2" t="n">
-        <v>45474</v>
+        <v>46143</v>
       </c>
       <c r="AB1" s="2" t="n">
-        <v>45444</v>
+        <v>46174</v>
       </c>
       <c r="AC1" s="2" t="n">
-        <v>45413</v>
+        <v>46204</v>
       </c>
       <c r="AD1" s="2" t="n">
-        <v>45383</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="2">
@@ -574,89 +573,89 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>66911850</v>
+        <v>2061777</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>813953256</v>
-      </c>
-      <c r="D2" s="4" t="inlineStr"/>
+        <v>2254333</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>2003303</v>
+      </c>
       <c r="E2" s="4" t="n">
-        <v>223175124</v>
+        <v>2246469</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>667378241</v>
+        <v>1750952</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>715405540</v>
+        <v>2256400</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>401983742</v>
+        <v>1904581</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>404986308</v>
+        <v>3619507</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>432603713</v>
+        <v>3734400</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>286576761</v>
+        <v>2351094</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>215517925</v>
+        <v>1574517</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>146544866</v>
+        <v>1654766</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>13406972</v>
+        <v>1437787</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>3330862</v>
+        <v>3158447</v>
       </c>
       <c r="P2" s="4" t="n">
         <v>3594591</v>
       </c>
       <c r="Q2" s="4" t="n">
-        <v>3158447</v>
+        <v>3330862</v>
       </c>
       <c r="R2" s="4" t="n">
-        <v>1437787</v>
+        <v>13406972</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>1654766</v>
+        <v>146544866</v>
       </c>
       <c r="T2" s="4" t="n">
-        <v>1574517</v>
+        <v>215517925</v>
       </c>
       <c r="U2" s="4" t="n">
-        <v>2351094</v>
+        <v>286576761</v>
       </c>
       <c r="V2" s="4" t="n">
-        <v>3734400</v>
+        <v>432603713</v>
       </c>
       <c r="W2" s="4" t="n">
-        <v>3619507</v>
+        <v>404986308</v>
       </c>
       <c r="X2" s="4" t="n">
-        <v>1904581</v>
+        <v>401983742</v>
       </c>
       <c r="Y2" s="4" t="n">
-        <v>2256400</v>
+        <v>715405540</v>
       </c>
       <c r="Z2" s="4" t="n">
-        <v>1750952</v>
+        <v>667378241</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>2246469</v>
-      </c>
-      <c r="AB2" s="4" t="n">
-        <v>2003303</v>
-      </c>
+        <v>223175124</v>
+      </c>
+      <c r="AB2" s="4" t="inlineStr"/>
       <c r="AC2" s="4" t="n">
-        <v>2254333</v>
+        <v>813953256</v>
       </c>
       <c r="AD2" s="4" t="n">
-        <v>2061777</v>
+        <v>66911850</v>
       </c>
     </row>
     <row r="3">
@@ -666,91 +665,91 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>2153964390.069834</v>
+        <v>27518291</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>35311239509.19695</v>
+        <v>27218005</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>41191769973.52393</v>
+        <v>29324981</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>16224090801.3501</v>
+        <v>32695951</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>14314585550.62995</v>
+        <v>20511722</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>14824345236.6</v>
+        <v>25608163</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>9893423824</v>
+        <v>400418974</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>8618085725</v>
+        <v>1151574886</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>7836081429</v>
+        <v>242429567</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>5207437836</v>
+        <v>163575081</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>4201591398</v>
+        <v>186343046</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>3662420283</v>
+        <v>623509970</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>813187580</v>
+        <v>414262477</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>680672117</v>
+        <v>609929285</v>
       </c>
       <c r="P3" s="4" t="n">
         <v>890716102</v>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>609929285</v>
+        <v>680672117</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>414262477</v>
+        <v>813187580</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>623509970</v>
+        <v>3662420283</v>
       </c>
       <c r="T3" s="4" t="n">
-        <v>186343046</v>
+        <v>4201591398</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>163575081</v>
+        <v>5207437836</v>
       </c>
       <c r="V3" s="4" t="n">
-        <v>242429567</v>
+        <v>7836081429</v>
       </c>
       <c r="W3" s="4" t="n">
-        <v>1151574886</v>
+        <v>8618085725</v>
       </c>
       <c r="X3" s="4" t="n">
-        <v>400418974</v>
+        <v>9893423824</v>
       </c>
       <c r="Y3" s="4" t="n">
-        <v>25608163</v>
+        <v>14824345236.6</v>
       </c>
       <c r="Z3" s="4" t="n">
-        <v>20511722</v>
+        <v>14314585550.62995</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>32695951</v>
+        <v>16224090801.3501</v>
       </c>
       <c r="AB3" s="4" t="n">
-        <v>29324981</v>
+        <v>41191769973.52393</v>
       </c>
       <c r="AC3" s="4" t="n">
-        <v>27218005</v>
+        <v>35311239509.19695</v>
       </c>
       <c r="AD3" s="4" t="n">
-        <v>27518291</v>
+        <v>2153964390.069834</v>
       </c>
     </row>
     <row r="4">
@@ -759,89 +758,89 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
-        <v>4643653.294101092</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>71270231.88350101</v>
-      </c>
+      <c r="B4" s="4" t="inlineStr"/>
+      <c r="C4" s="4" t="inlineStr"/>
       <c r="D4" s="4" t="n">
-        <v>168606377.3318905</v>
+        <v>3426347.046664575</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>104134617.7552582</v>
+        <v>5892804.610869758</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>70491732.37979549</v>
+        <v>5779421.203383358</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>194183228.7263323</v>
+        <v>12884285.28089719</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>257142376.9454393</v>
+        <v>166374082.9356964</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>198954417.1166546</v>
+        <v>483080397.41767</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>326092406.1199697</v>
+        <v>24713166.19906684</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>208418609.9076059</v>
+        <v>16912116.76384585</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>105076974.4656361</v>
+        <v>13609119.07444031</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>55962810.43918746</v>
+        <v>18112285.31570254</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>28400342.36631728</v>
+        <v>14619056.35708779</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>18545993.77710526</v>
+        <v>20571024.64744093</v>
       </c>
       <c r="P4" s="4" t="n">
         <v>22219040.75499423</v>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>20571024.64744093</v>
+        <v>18545993.77710526</v>
       </c>
       <c r="R4" s="4" t="n">
-        <v>14619056.35708779</v>
+        <v>28400342.36631728</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>18112285.31570254</v>
+        <v>55962810.43918746</v>
       </c>
       <c r="T4" s="4" t="n">
-        <v>13609119.07444031</v>
+        <v>105076974.4656361</v>
       </c>
       <c r="U4" s="4" t="n">
-        <v>16912116.76384585</v>
+        <v>208418609.9076059</v>
       </c>
       <c r="V4" s="4" t="n">
-        <v>24713166.19906684</v>
+        <v>326092406.1199697</v>
       </c>
       <c r="W4" s="4" t="n">
-        <v>483080397.41767</v>
+        <v>198954417.1166546</v>
       </c>
       <c r="X4" s="4" t="n">
-        <v>166374082.9356964</v>
+        <v>257142376.9454393</v>
       </c>
       <c r="Y4" s="4" t="n">
-        <v>12884285.28089719</v>
+        <v>194183228.7263323</v>
       </c>
       <c r="Z4" s="4" t="n">
-        <v>5779421.203383358</v>
+        <v>70491732.37979549</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>5892804.610869758</v>
+        <v>104134617.7552582</v>
       </c>
       <c r="AB4" s="4" t="n">
-        <v>3426347.046664575</v>
-      </c>
-      <c r="AC4" s="4" t="inlineStr"/>
-      <c r="AD4" s="4" t="inlineStr"/>
+        <v>168606377.3318905</v>
+      </c>
+      <c r="AC4" s="4" t="n">
+        <v>71270231.88350101</v>
+      </c>
+      <c r="AD4" s="4" t="n">
+        <v>4643653.294101092</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -850,91 +849,91 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>316771939.4218129</v>
+        <v>60398681.77173485</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>6154151700.872653</v>
+        <v>98195346.27512182</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>12755264111.1305</v>
+        <v>202023049.8246841</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>6492207881.553761</v>
+        <v>903061516.0529358</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>8189860829.165617</v>
+        <v>762974977.3386035</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>11599634363.50984</v>
+        <v>1378405288.69402</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>8015235516.373124</v>
+        <v>4222070317.766811</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>7100841879.671216</v>
+        <v>3075755417.271811</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>6174994043.049665</v>
+        <v>3749403735.677081</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>4024779119.682765</v>
+        <v>2218222253.983505</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>4069425640.019949</v>
+        <v>1537314862.961097</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>1983806752.908436</v>
+        <v>4135190845.901176</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>1004078978.579967</v>
+        <v>1195094090.880569</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>1056239818.3701</v>
+        <v>1214145559.28363</v>
       </c>
       <c r="P5" s="4" t="n">
         <v>1577665235.780081</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>1214145559.28363</v>
+        <v>1056239818.3701</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>1195094090.880569</v>
+        <v>1004078978.579967</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>4135190845.901176</v>
+        <v>1983806752.908436</v>
       </c>
       <c r="T5" s="4" t="n">
-        <v>1537314862.961097</v>
+        <v>4069425640.019949</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>2218222253.983505</v>
+        <v>4024779119.682765</v>
       </c>
       <c r="V5" s="4" t="n">
-        <v>3749403735.677081</v>
+        <v>6174994043.049665</v>
       </c>
       <c r="W5" s="4" t="n">
-        <v>3075755417.271811</v>
+        <v>7100841879.671216</v>
       </c>
       <c r="X5" s="4" t="n">
-        <v>4222070317.766811</v>
+        <v>8015235516.373124</v>
       </c>
       <c r="Y5" s="4" t="n">
-        <v>1378405288.69402</v>
+        <v>11599634363.50984</v>
       </c>
       <c r="Z5" s="4" t="n">
-        <v>762974977.3386035</v>
+        <v>8189860829.165617</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>903061516.0529358</v>
+        <v>6492207881.553761</v>
       </c>
       <c r="AB5" s="4" t="n">
-        <v>202023049.8246841</v>
+        <v>12755264111.1305</v>
       </c>
       <c r="AC5" s="4" t="n">
-        <v>98195346.27512182</v>
+        <v>6154151700.872653</v>
       </c>
       <c r="AD5" s="4" t="n">
-        <v>60398681.77173485</v>
+        <v>316771939.4218129</v>
       </c>
     </row>
   </sheetData>
@@ -971,34 +970,34 @@
         </is>
       </c>
       <c r="B1" s="2" t="n">
+        <v>45383</v>
+      </c>
+      <c r="C1" s="2" t="n">
+        <v>45474</v>
+      </c>
+      <c r="D1" s="2" t="n">
+        <v>45566</v>
+      </c>
+      <c r="E1" s="2" t="n">
+        <v>45658</v>
+      </c>
+      <c r="F1" s="2" t="n">
+        <v>45748</v>
+      </c>
+      <c r="G1" s="2" t="n">
+        <v>45839</v>
+      </c>
+      <c r="H1" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I1" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="J1" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="K1" s="2" t="n">
         <v>46204</v>
-      </c>
-      <c r="C1" s="2" t="n">
-        <v>46113</v>
-      </c>
-      <c r="D1" s="2" t="n">
-        <v>46023</v>
-      </c>
-      <c r="E1" s="2" t="n">
-        <v>45931</v>
-      </c>
-      <c r="F1" s="2" t="n">
-        <v>45839</v>
-      </c>
-      <c r="G1" s="2" t="n">
-        <v>45748</v>
-      </c>
-      <c r="H1" s="2" t="n">
-        <v>45658</v>
-      </c>
-      <c r="I1" s="2" t="n">
-        <v>45566</v>
-      </c>
-      <c r="J1" s="2" t="n">
-        <v>45474</v>
-      </c>
-      <c r="K1" s="2" t="n">
-        <v>45383</v>
       </c>
     </row>
     <row r="2">
@@ -1008,34 +1007,34 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
+        <v>6319413</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>6253821</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>9258488</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>5580377</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>8190825</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>163282700</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>934698399</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>1522375590</v>
+      </c>
+      <c r="J2" s="4" t="n">
+        <v>890553365</v>
+      </c>
+      <c r="K2" s="4" t="n">
         <v>880865106</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>890553365</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>1522375590</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>934698399</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>163282700</v>
-      </c>
-      <c r="G2" s="4" t="n">
-        <v>8190825</v>
-      </c>
-      <c r="H2" s="4" t="n">
-        <v>5580377</v>
-      </c>
-      <c r="I2" s="4" t="n">
-        <v>9258488</v>
-      </c>
-      <c r="J2" s="4" t="n">
-        <v>6253821</v>
-      </c>
-      <c r="K2" s="4" t="n">
-        <v>6319413</v>
       </c>
     </row>
     <row r="3">
@@ -1045,34 +1044,34 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
+        <v>84061277</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>78815836</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>1794423427</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>973428097</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>1914907864</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>5156279980</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>17245110663</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>33335854785.6</v>
+      </c>
+      <c r="J3" s="4" t="n">
+        <v>71730446325.50398</v>
+      </c>
+      <c r="K3" s="4" t="n">
         <v>37465203899.26678</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>71730446325.50398</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>33335854785.6</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>17245110663</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>5156279980</v>
-      </c>
-      <c r="G3" s="4" t="n">
-        <v>1914907864</v>
-      </c>
-      <c r="H3" s="4" t="n">
-        <v>973428097</v>
-      </c>
-      <c r="I3" s="4" t="n">
-        <v>1794423427</v>
-      </c>
-      <c r="J3" s="4" t="n">
-        <v>78815836</v>
-      </c>
-      <c r="K3" s="4" t="n">
-        <v>84061277</v>
       </c>
     </row>
     <row r="4">
@@ -1082,34 +1081,34 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
+        <v>3426347.046664575</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>24556511.09515031</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>674167646.5524333</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>48633521.1539887</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>57409121.75952295</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>102909146.58261</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>639587990.4932117</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>650280022.7884263</v>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>343232727.4669442</v>
+      </c>
+      <c r="K4" s="4" t="n">
         <v>75913885.1776021</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>343232727.4669442</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>650280022.7884263</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>639587990.4932117</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>102909146.58261</v>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>57409121.75952295</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>48633521.1539887</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>674167646.5524333</v>
-      </c>
-      <c r="J4" s="4" t="n">
-        <v>24556511.09515031</v>
-      </c>
-      <c r="K4" s="4" t="n">
-        <v>3426347.046664575</v>
       </c>
     </row>
     <row r="5">
@@ -1119,34 +1118,34 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
+        <v>360617077.8715408</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>3044441782.085559</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>11047229470.7157</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>7890727962.845778</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>3986904885.94428</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>4044125549.858503</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>14269198802.75238</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>26715711759.55418</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>27437332821.84988</v>
+      </c>
+      <c r="K5" s="4" t="n">
         <v>6470923640.294466</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>27437332821.84988</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>26715711759.55418</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>14269198802.75238</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>4044125549.858503</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>3986904885.94428</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>7890727962.845778</v>
-      </c>
-      <c r="I5" s="4" t="n">
-        <v>11047229470.7157</v>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>3044441782.085559</v>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>360617077.8715408</v>
       </c>
     </row>
   </sheetData>

--- a/prediction_market_volumes.xlsx
+++ b/prediction_market_volumes.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Weekly" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E125"/>
+  <dimension ref="A1:E127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -619,7 +619,7 @@
         <v>9048872</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>679273.0137536518</v>
+        <v>679273.013753654</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>40345603.55045231</v>
@@ -636,7 +636,7 @@
         <v>5531106</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1352600.965417855</v>
+        <v>1352600.965417854</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>42557204.59761641</v>
@@ -653,7 +653,7 @@
         <v>7683018</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>1394218.981311467</v>
+        <v>1394218.981311469</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>81460075.37423241</v>
@@ -670,7 +670,7 @@
         <v>6711626</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1789531.259764357</v>
+        <v>1789531.259764356</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>90056795.85345295</v>
@@ -704,7 +704,7 @@
         <v>6176189</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>636470.7846585037</v>
+        <v>636470.7846585028</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>199901580.1187507</v>
@@ -721,7 +721,7 @@
         <v>6061251</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>837261.4918236855</v>
+        <v>837261.4918236866</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>290626968.092454</v>
@@ -738,7 +738,7 @@
         <v>7133914</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1247812.020178272</v>
+        <v>1247812.020178271</v>
       </c>
       <c r="E18" s="3" t="n">
         <v>237099244.6621625</v>
@@ -755,7 +755,7 @@
         <v>5925308</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>946804.8082189256</v>
+        <v>946804.8082189228</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>206402897.1905403</v>
@@ -806,7 +806,7 @@
         <v>4086777</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>1778281.087056471</v>
+        <v>1778281.08705647</v>
       </c>
       <c r="E22" s="3" t="n">
         <v>170916966.233661</v>
@@ -823,7 +823,7 @@
         <v>4359143</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1637955.655301908</v>
+        <v>1637955.655301911</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>179169675.6689627</v>
@@ -840,7 +840,7 @@
         <v>5886476</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>2125360.537650111</v>
+        <v>2125360.537650114</v>
       </c>
       <c r="E24" s="3" t="n">
         <v>198170419.9062966</v>
@@ -857,7 +857,7 @@
         <v>5760199</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>2896676.303012701</v>
+        <v>2896676.303012702</v>
       </c>
       <c r="E25" s="3" t="n">
         <v>180785074.5757283</v>
@@ -891,10 +891,10 @@
         <v>5290382</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>3113115.855708822</v>
+        <v>3113115.855708824</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>574014825.6289338</v>
+        <v>574014825.6289339</v>
       </c>
     </row>
     <row r="28">
@@ -908,10 +908,10 @@
         <v>13740138</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>6389307.114904336</v>
+        <v>6389307.114904339</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>811644357.4050939</v>
+        <v>811644357.405094</v>
       </c>
     </row>
     <row r="29">
@@ -925,7 +925,7 @@
         <v>47437496</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>9235264.478411036</v>
+        <v>9235264.478411034</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>890073919.2381443</v>
@@ -942,7 +942,7 @@
         <v>100976912</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>14322499.13686397</v>
+        <v>14322499.13686396</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>1240887102.080215</v>
@@ -993,7 +993,7 @@
         <v>201070993</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>23230777.70474211</v>
+        <v>23230777.7047421</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>728972374.7910814</v>
@@ -1010,7 +1010,7 @@
         <v>127196751</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>9322021.987109289</v>
+        <v>9322021.987109292</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>558989131.8217986</v>
@@ -1027,10 +1027,10 @@
         <v>73346838</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>8691271.318891879</v>
+        <v>8691271.318891881</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>556374763.5437212</v>
+        <v>556374763.5437213</v>
       </c>
     </row>
     <row r="36">
@@ -1044,7 +1044,7 @@
         <v>79089255</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>6909634.246601928</v>
+        <v>6909634.246601927</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>676636808.6240612</v>
@@ -1061,10 +1061,10 @@
         <v>52298975</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>5051974.070174427</v>
+        <v>5051974.070174433</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>562729649.6132931</v>
+        <v>562729649.6132929</v>
       </c>
     </row>
     <row r="38">
@@ -1078,10 +1078,10 @@
         <v>48998815</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>4351394.647259925</v>
+        <v>4351394.647259926</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>773867076.8987241</v>
+        <v>773867076.8987242</v>
       </c>
     </row>
     <row r="39">
@@ -1095,7 +1095,7 @@
         <v>28069797</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>3889838.511196571</v>
+        <v>3889838.511196566</v>
       </c>
       <c r="E39" s="3" t="n">
         <v>881815833.9494522</v>
@@ -1112,10 +1112,10 @@
         <v>33972725</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>4510324.723833986</v>
+        <v>4510324.723833989</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>854354366.5915501</v>
+        <v>854354366.5915502</v>
       </c>
     </row>
     <row r="41">
@@ -1129,7 +1129,7 @@
         <v>31503973</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>4117146.669979074</v>
+        <v>4117146.669979073</v>
       </c>
       <c r="E41" s="3" t="n">
         <v>498113289.7398963</v>
@@ -1146,7 +1146,7 @@
         <v>36616735</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>4554850.646304653</v>
+        <v>4554850.646304652</v>
       </c>
       <c r="E42" s="3" t="n">
         <v>630452073.2696528</v>
@@ -1163,7 +1163,7 @@
         <v>58757479</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>4024434.241910749</v>
+        <v>4024434.241910751</v>
       </c>
       <c r="E43" s="3" t="n">
         <v>666825531.0645243</v>
@@ -1180,7 +1180,7 @@
         <v>36696894</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>4215685.205651361</v>
+        <v>4215685.205651367</v>
       </c>
       <c r="E44" s="3" t="n">
         <v>422831359.9094315</v>
@@ -1214,7 +1214,7 @@
         <v>41557967</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>3434310.554087616</v>
+        <v>3434310.554087613</v>
       </c>
       <c r="E46" s="3" t="n">
         <v>409757640.7664339</v>
@@ -1231,7 +1231,7 @@
         <v>37735400</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>3202163.195904875</v>
+        <v>3202163.19590487</v>
       </c>
       <c r="E47" s="3" t="n">
         <v>451487775.1408475</v>
@@ -1248,7 +1248,7 @@
         <v>39080271</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>3145931.810803362</v>
+        <v>3145931.810803368</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>381347162.8763123</v>
@@ -1265,7 +1265,7 @@
         <v>42610773</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>3592044.552066014</v>
+        <v>3592044.552066017</v>
       </c>
       <c r="E49" s="3" t="n">
         <v>302058879.6471181</v>
@@ -1299,7 +1299,7 @@
         <v>221041956</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>3381837.451397219</v>
+        <v>3381837.45139722</v>
       </c>
       <c r="E51" s="3" t="n">
         <v>303186827.5061712</v>
@@ -1316,7 +1316,7 @@
         <v>195231766</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>3755710.03162159</v>
+        <v>3755710.031621587</v>
       </c>
       <c r="E52" s="3" t="n">
         <v>339050017.8761171</v>
@@ -1333,7 +1333,7 @@
         <v>131901956</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>3478873.101296134</v>
+        <v>3478873.101296135</v>
       </c>
       <c r="E53" s="3" t="n">
         <v>2865235912.887944</v>
@@ -1367,7 +1367,7 @@
         <v>55492642</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>2989687.338569943</v>
+        <v>2989687.338569944</v>
       </c>
       <c r="E55" s="3" t="n">
         <v>213951244.0051962</v>
@@ -1401,7 +1401,7 @@
         <v>123600695</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>3902844.382247422</v>
+        <v>3902844.382247423</v>
       </c>
       <c r="E57" s="3" t="n">
         <v>399474890.9205555</v>
@@ -1418,7 +1418,7 @@
         <v>122461192</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>5939479.602621392</v>
+        <v>5939479.602621391</v>
       </c>
       <c r="E58" s="3" t="n">
         <v>356969877.4481152</v>
@@ -1435,7 +1435,7 @@
         <v>161897553</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>5056264.504399238</v>
+        <v>5056264.504399237</v>
       </c>
       <c r="E59" s="3" t="n">
         <v>342828235.934832</v>
@@ -1605,7 +1605,7 @@
         <v>156842629</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>5074991.354539377</v>
+        <v>5074991.354539378</v>
       </c>
       <c r="E69" s="3" t="n">
         <v>240655290.1908669</v>
@@ -1622,7 +1622,7 @@
         <v>143028757</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>5196914.435681973</v>
+        <v>5196914.435681974</v>
       </c>
       <c r="E70" s="3" t="n">
         <v>280321023.2247133</v>
@@ -1639,7 +1639,7 @@
         <v>151025682</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>5424955.823662447</v>
+        <v>5424955.823662448</v>
       </c>
       <c r="E71" s="3" t="n">
         <v>212809721.8283699</v>
@@ -1656,7 +1656,7 @@
         <v>178682902</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>6562706.243883893</v>
+        <v>6562706.243883894</v>
       </c>
       <c r="E72" s="3" t="n">
         <v>256005733.4759509</v>
@@ -1690,7 +1690,7 @@
         <v>296524006</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>9392010.686156249</v>
+        <v>9392010.686156243</v>
       </c>
       <c r="E74" s="3" t="n">
         <v>265462210.6642144</v>
@@ -1724,7 +1724,7 @@
         <v>561997258</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>10195906.28957781</v>
+        <v>10195906.2895778</v>
       </c>
       <c r="E76" s="3" t="n">
         <v>334096492.3303622</v>
@@ -1846,7 +1846,7 @@
         <v>51712146.89997102</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>1107382200.950277</v>
+        <v>1107382200.950278</v>
       </c>
     </row>
     <row r="84">
@@ -1860,10 +1860,10 @@
         <v>1304733534</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>50046053.40087847</v>
+        <v>50046053.40087848</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>1001788838.169827</v>
+        <v>1001788838.169828</v>
       </c>
     </row>
     <row r="85">
@@ -1877,10 +1877,10 @@
         <v>1240160888</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>29797035.72113394</v>
+        <v>29797035.72113393</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>952488910.3862704</v>
+        <v>952488910.3862706</v>
       </c>
     </row>
     <row r="86">
@@ -1894,7 +1894,7 @@
         <v>1144695344</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>37940211.01568554</v>
+        <v>37940211.01568555</v>
       </c>
       <c r="E86" s="3" t="n">
         <v>986575712.049724</v>
@@ -1911,10 +1911,10 @@
         <v>1517848070</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>90635309.76990804</v>
+        <v>90635309.76990797</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>1083925659.076943</v>
+        <v>1083925659.076944</v>
       </c>
     </row>
     <row r="88">
@@ -1928,7 +1928,7 @@
         <v>1295551558</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>38099183.19017645</v>
+        <v>38099183.19017644</v>
       </c>
       <c r="E88" s="3" t="n">
         <v>1292615925.180026</v>
@@ -1979,7 +1979,7 @@
         <v>1707747150</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>95084723.2172154</v>
+        <v>95084723.21721536</v>
       </c>
       <c r="E91" s="3" t="n">
         <v>1094963942.824699</v>
@@ -1996,10 +1996,10 @@
         <v>1978665806</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>83162416.608294</v>
+        <v>83162416.60829398</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>1445093135.868077</v>
+        <v>1445093135.868078</v>
       </c>
     </row>
     <row r="93">
@@ -2030,10 +2030,10 @@
         <v>2153060916</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>58519229.80581053</v>
+        <v>58519229.80581054</v>
       </c>
       <c r="E94" s="3" t="n">
-        <v>1758081904.790645</v>
+        <v>1758081904.790646</v>
       </c>
     </row>
     <row r="95">
@@ -2047,7 +2047,7 @@
         <v>2257916803</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>45435913.92628626</v>
+        <v>45435913.92628625</v>
       </c>
       <c r="E95" s="3" t="n">
         <v>1756113805.167978</v>
@@ -2064,10 +2064,10 @@
         <v>2195101449</v>
       </c>
       <c r="D96" s="3" t="n">
-        <v>43327364.04695514</v>
+        <v>43327364.04695515</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>2082838477.86191</v>
+        <v>2082838477.861911</v>
       </c>
     </row>
     <row r="97">
@@ -2081,10 +2081,10 @@
         <v>2488710517</v>
       </c>
       <c r="D97" s="3" t="n">
-        <v>51070111.59028681</v>
+        <v>51070111.59028682</v>
       </c>
       <c r="E97" s="3" t="n">
-        <v>1915385557.726192</v>
+        <v>1915385557.726193</v>
       </c>
     </row>
     <row r="98">
@@ -2118,7 +2118,7 @@
         <v>70094316.22315279</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>1819961193.763658</v>
+        <v>1819961193.763659</v>
       </c>
     </row>
     <row r="100">
@@ -2132,7 +2132,7 @@
         <v>2384587100</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>61003904.12516204</v>
+        <v>61003904.12516203</v>
       </c>
       <c r="E100" s="3" t="n">
         <v>2400246464.277964</v>
@@ -2152,7 +2152,7 @@
         <v>62762256.8671192</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>2496400573.622877</v>
+        <v>2496400573.622876</v>
       </c>
     </row>
     <row r="102">
@@ -2166,7 +2166,7 @@
         <v>2934749298.45</v>
       </c>
       <c r="D102" s="3" t="n">
-        <v>61651178.88210624</v>
+        <v>61651178.88210625</v>
       </c>
       <c r="E102" s="3" t="n">
         <v>2344271508.347281</v>
@@ -2186,7 +2186,7 @@
         <v>31116036.54869318</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>2544656858.732326</v>
+        <v>2544656858.732325</v>
       </c>
     </row>
     <row r="104">
@@ -2203,7 +2203,7 @@
         <v>20878207.48838676</v>
       </c>
       <c r="E104" s="3" t="n">
-        <v>2241717048.837049</v>
+        <v>2241717048.837048</v>
       </c>
     </row>
     <row r="105">
@@ -2220,7 +2220,7 @@
         <v>17775548.94002695</v>
       </c>
       <c r="E105" s="3" t="n">
-        <v>1972588373.97031</v>
+        <v>1972588373.970309</v>
       </c>
     </row>
     <row r="106">
@@ -2237,7 +2237,7 @@
         <v>22028553.06314011</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>2475772644.086282</v>
+        <v>2475772644.086281</v>
       </c>
     </row>
     <row r="107">
@@ -2248,13 +2248,13 @@
         <v>148255665</v>
       </c>
       <c r="C107" s="3" t="n">
-        <v>3059030025.749977</v>
+        <v>3059030025.749976</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>21480299.37743044</v>
+        <v>21480299.37743045</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>2041883298.176268</v>
+        <v>2041883298.176267</v>
       </c>
     </row>
     <row r="108">
@@ -2271,7 +2271,7 @@
         <v>14955754.79899644</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>1961724698.107497</v>
+        <v>1961724698.107498</v>
       </c>
     </row>
     <row r="109">
@@ -2282,7 +2282,7 @@
         <v>165933791</v>
       </c>
       <c r="C109" s="3" t="n">
-        <v>3809209066.749989</v>
+        <v>3809209066.74999</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>12027125.14022851</v>
@@ -2299,7 +2299,7 @@
         <v>161267757</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>4133679757.789968</v>
+        <v>4133679757.789969</v>
       </c>
       <c r="D110" s="3" t="n">
         <v>27355398.91991135</v>
@@ -2322,7 +2322,7 @@
         <v>31029689.81640879</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>1578244532.68918</v>
+        <v>1578244532.689181</v>
       </c>
     </row>
     <row r="112">
@@ -2337,7 +2337,7 @@
         <v>24537576.84382511</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>1640677853.554454</v>
+        <v>1640677853.554453</v>
       </c>
     </row>
     <row r="113">
@@ -2367,7 +2367,7 @@
         <v>22248689.0447677</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>1909567297.135419</v>
+        <v>1909567297.135418</v>
       </c>
     </row>
     <row r="115">
@@ -2397,7 +2397,7 @@
         <v>41843203.2470731</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>2935947795.337724</v>
+        <v>2935947795.337725</v>
       </c>
     </row>
     <row r="117">
@@ -2412,7 +2412,7 @@
         <v>41811783.81721697</v>
       </c>
       <c r="E117" s="3" t="n">
-        <v>2674557473.817702</v>
+        <v>2674557473.817704</v>
       </c>
     </row>
     <row r="118">
@@ -2438,13 +2438,13 @@
         <v>179989782</v>
       </c>
       <c r="C119" s="3" t="n">
-        <v>9915304929.389122</v>
+        <v>9915304929.388985</v>
       </c>
       <c r="D119" s="3" t="n">
-        <v>21021856.68113643</v>
+        <v>21021856.68113641</v>
       </c>
       <c r="E119" s="3" t="n">
-        <v>2335080636.464052</v>
+        <v>2335080636.464053</v>
       </c>
     </row>
     <row r="120">
@@ -2455,10 +2455,10 @@
         <v>219987570</v>
       </c>
       <c r="C120" s="3" t="n">
-        <v>9120491349.079369</v>
+        <v>9120491349.079613</v>
       </c>
       <c r="D120" s="3" t="n">
-        <v>19394051.90348686</v>
+        <v>19394051.90348685</v>
       </c>
       <c r="E120" s="3" t="n">
         <v>1757616928.25561</v>
@@ -2472,7 +2472,7 @@
         <v>194372614</v>
       </c>
       <c r="C121" s="3" t="n">
-        <v>7893433708.82933</v>
+        <v>7893433708.829004</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>15960467.0583101</v>
@@ -2489,7 +2489,7 @@
         <v>219603290</v>
       </c>
       <c r="C122" s="3" t="n">
-        <v>8382009521.899131</v>
+        <v>8382009521.899019</v>
       </c>
       <c r="D122" s="3" t="n">
         <v>14893856.24056764</v>
@@ -2506,13 +2506,13 @@
         <v>209378748</v>
       </c>
       <c r="C123" s="3" t="n">
-        <v>8111261310.279154</v>
+        <v>8111261310.279717</v>
       </c>
       <c r="D123" s="3" t="n">
-        <v>16752787.96765504</v>
+        <v>16752787.96765505</v>
       </c>
       <c r="E123" s="3" t="n">
-        <v>914203447.7782226</v>
+        <v>914203447.7782228</v>
       </c>
     </row>
     <row r="124">
@@ -2523,10 +2523,10 @@
         <v>212014152</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>8684353096.189138</v>
+        <v>8684353096.191481</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>6493523.832390472</v>
+        <v>16862788.83239046</v>
       </c>
       <c r="E124" s="3" t="n">
         <v>1023148090.754371</v>
@@ -2537,14 +2537,48 @@
         <v>46251</v>
       </c>
       <c r="B125" s="3" t="n">
-        <v>12634024</v>
-      </c>
-      <c r="C125" s="3" t="inlineStr"/>
+        <v>227398376</v>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>9100167289.259687</v>
+      </c>
       <c r="D125" s="3" t="n">
-        <v>96941.99394728668</v>
+        <v>20417465.82520187</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>33228875.98398358</v>
+        <v>1148702568.307406</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B126" s="3" t="n">
+        <v>210689185</v>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>10181384288.29883</v>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>18977964.76603964</v>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>1046137034.001078</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B127" s="3" t="n">
+        <v>28667946</v>
+      </c>
+      <c r="C127" s="3" t="inlineStr"/>
+      <c r="D127" s="3" t="n">
+        <v>447248.4570488976</v>
+      </c>
+      <c r="E127" s="3" t="n">
+        <v>127095383.0856253</v>
       </c>
     </row>
   </sheetData>
